--- a/output/laminas_comunales/comunal_p_basica_a_2018_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_p_basica_a_2018_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,82 +384,1882 @@
         </is>
       </c>
       <c r="C2">
-        <v>58.7628860473633</v>
+        <v>100201.890625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.2831840515137</v>
+        <v>99681.4296875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C4">
-        <v>20.9728870391846</v>
+        <v>97864.953125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C5">
-        <v>20.0216255187988</v>
+        <v>93532.140625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C6">
-        <v>18.2406215667725</v>
+        <v>92073.3828125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>86589.3125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>84480.9765625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>84333.984375</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>83900.0390625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Iquique</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C11">
+        <v>81224.6875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>81128.921875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>79216.5078125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>79134.15625</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>77685.9375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>76918.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>76721.4296875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>76387.90625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>75775.234375</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>75035.921875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>74697.2734375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>74407.5390625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>73082.5234375</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>72126.8671875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>70959.3828125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>70912.7421875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>70880.203125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>70319.125</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>69849.0625</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>68952.1875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>67690.9453125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>67106.0234375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>64226</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>63996.26953125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>62616.54296875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>60949.9453125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>60376.671875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>59856.13671875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>59594.23046875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>55740.296875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>54991.66796875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>53289.2109375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>49888.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>77.94117736816411</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>70.58823394775391</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>66.6666641235352</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>58.7628860473633</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>55.0131912231445</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>53.6628723144531</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>53.4883728027344</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>52.2256278991699</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>51.3674201965332</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>50.7489967346191</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>50.5263175964355</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>49.8373985290527</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>48.9795913696289</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>48.9071044921875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>48.1751823425293</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>47.2527465820312</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>46.5174140930176</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>46.2882080078125</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>45.9821434020996</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>45.7317085266113</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>45.6140365600586</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>44.9541282653809</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>44.8979606628418</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>44.797176361084</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>44.4444427490234</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>43.6363639831543</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>43.4977569580078</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>43.1034469604492</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>43.0062637329102</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>42.1562232971191</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>42.1091270446777</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>41.8879051208496</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>41.7852516174316</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>41.2121200561523</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>40.2934875488281</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>40.2298851013184</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>38.9473686218262</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>38.461540222168</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>38.19775390625</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>38.1752700805664</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>38.1147537231445</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>38.0208320617676</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>36.6576805114746</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>36.2831840515137</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>34.8837203979492</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>34.4827575683594</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>34.0807189941406</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>33.3485412597656</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>33.0910110473633</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>32.989688873291</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>32.0987663269043</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>31.6091957092285</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>30.6878299713135</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>29.4642848968506</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>29.2318630218506</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>27.2727279663086</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>27.1857929229736</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>25.3269920349121</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>23.8532104492188</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>23.3576641082764</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>21.5699214935303</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>21.3930339813232</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>20.9728870391846</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>20.0216255187988</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>18.5975608825684</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>18.2406215667725</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>17.6470584869385</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>17.251651763916</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>15.6527051925659</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>14.8247976303101</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>14.4308938980103</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>13.7655057907104</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>13.0902862548828</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>12.9548759460449</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C121">
         <v>12.609564781189</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>11.764705657959</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>11.2734861373901</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>10.5590057373047</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>9.604361534118651</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>8.606557846069339</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>6.92290163040161</v>
       </c>
     </row>
   </sheetData>
